--- a/artfynd/A 22010-2025 artfynd.xlsx
+++ b/artfynd/A 22010-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,38 +675,33 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6296611</v>
+        <v>333192</v>
       </c>
       <c r="B2" t="n">
-        <v>98538</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106499</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>224913</v>
+        <v>981</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig backsippa</t>
+          <t>Vit sminkrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris subsp. vulgaris</t>
+          <t>Buglossoides arvensis var. arvensis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -720,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>645469.858450908</v>
+        <v>645470</v>
       </c>
       <c r="R2" t="n">
-        <v>6623963.425324108</v>
+        <v>6623963</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -750,27 +745,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2008-04-27</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-05-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2008-04-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-05-03</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Kraftig minskning från 102 ex -07 till 42 -08. igenväxning av tall.</t>
+          <t>200 m N Dampeboda</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,7 +769,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Gräsmark</t>
+          <t>Slänt vid åker</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -795,22 +780,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Thommy Åkerberg, Michael Åkerberg</t>
+          <t>Thommy Åkerberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>333192</v>
+        <v>3925186</v>
       </c>
       <c r="B3" t="n">
-        <v>103492</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>102241</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -818,24 +798,24 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>981</v>
+        <v>221235</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vit sminkrot</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Buglossoides arvensis var. arvensis</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>blomning</t>
@@ -847,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>645469.858450908</v>
+        <v>645470</v>
       </c>
       <c r="R3" t="n">
-        <v>6623963.425324108</v>
+        <v>6623963</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -880,24 +860,14 @@
           <t>2008-05-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2008-05-03</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>200 m N Dampeboda</t>
+          <t>500 m NO Dampeboda</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,7 +881,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Slänt vid åker</t>
+          <t>Asplund</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -929,58 +899,51 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3925186</v>
+        <v>6748708</v>
       </c>
       <c r="B4" t="n">
-        <v>99397</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107517</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221235</v>
+        <v>221849</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Dampebovik, Upl</t>
+          <t>Dampeboda, Skokloster, 300m N, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>645469.858450908</v>
+        <v>645473</v>
       </c>
       <c r="R4" t="n">
-        <v>6623963.425324108</v>
+        <v>6624000</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1004,27 +967,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2008-05-03</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1986-07-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2008-05-03</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>500 m NO Dampeboda</t>
+          <t>1986-07-25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,56 +983,50 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Asplund</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Thommy Åkerberg</t>
+          <t>Torbjörn Persson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Thommy Åkerberg</t>
+          <t>Torbjörn Persson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>6748701</v>
+        <v>6748698</v>
       </c>
       <c r="B5" t="n">
-        <v>98539</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100798</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>224913</v>
+        <v>222617</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vanlig backsippa</t>
+          <t>Flentimotej</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pulsatilla vulgaris subsp. vulgaris</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Phleum phleoides</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) H. Karst.</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -1095,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>645473.4715685523</v>
+        <v>645473</v>
       </c>
       <c r="R5" t="n">
-        <v>6624000.417793456</v>
+        <v>6624000</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1128,19 +1070,9 @@
           <t>1986-07-25</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>1986-07-25</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1167,15 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>6748698</v>
+        <v>6748697</v>
       </c>
       <c r="B6" t="n">
-        <v>97952</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107063</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1183,23 +1110,19 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222617</v>
+        <v>224354</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Flentimotej</t>
+          <t>Vanlig axveronika</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phleum phleoides</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(L.) H. Karst.</t>
-        </is>
-      </c>
+          <t>Veronica spicata subsp. spicata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1210,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>645473.4715685523</v>
+        <v>645473</v>
       </c>
       <c r="R6" t="n">
-        <v>6624000.417793456</v>
+        <v>6624000</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1243,19 +1166,9 @@
           <t>1986-07-25</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>1986-07-25</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1282,52 +1195,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6748697</v>
+        <v>6296611</v>
       </c>
       <c r="B7" t="n">
-        <v>104035</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>224354</v>
+        <v>224913</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vanlig axveronika</t>
+          <t>Vanlig backsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Veronica spicata subsp. spicata</t>
+          <t>Pulsatilla vulgaris subsp. vulgaris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Dampeboda, Skokloster, 300m N, Upl</t>
+          <t>Dampebovik, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>645473.4715685523</v>
+        <v>645470</v>
       </c>
       <c r="R7" t="n">
-        <v>6624000.417793456</v>
+        <v>6623963</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1351,22 +1265,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>1986-07-25</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-04-27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1986-07-25</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-04-27</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Kraftig minskning från 102 ex -07 till 42 -08. igenväxning av tall.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,55 +1286,51 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Gräsmark</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Torbjörn Persson</t>
+          <t>Thommy Åkerberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Torbjörn Persson</t>
+          <t>Thommy Åkerberg, Michael Åkerberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>6748708</v>
+        <v>6748701</v>
       </c>
       <c r="B8" t="n">
-        <v>104404</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221849</v>
+        <v>224913</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Vanlig backsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Pulsatilla vulgaris subsp. vulgaris</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1436,10 +1341,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>645473.4715685523</v>
+        <v>645473</v>
       </c>
       <c r="R8" t="n">
-        <v>6624000.417793456</v>
+        <v>6624000</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1469,19 +1374,9 @@
           <t>1986-07-25</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>1986-07-25</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1508,15 +1403,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>87235164</v>
+        <v>87235162</v>
       </c>
       <c r="B9" t="n">
-        <v>98539</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101348</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,7 +1429,7 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1549,7 +1439,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1558,13 +1448,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>645454.7374577721</v>
+        <v>645443</v>
       </c>
       <c r="R9" t="n">
-        <v>6623988.076013238</v>
+        <v>6624030</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1591,24 +1481,14 @@
           <t>2020-05-15</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2020-05-15</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>267 stjälkar (de flesta blommande, men även i knopp och överblommade), i och vid en liten glänta och intill ett par körvägar i sandtallskog.</t>
+          <t>20 stjälkar (de flesta överblommade, men även i knopp och blommande), på och precis intill en solexponerad, gammal körväg på sandig mark.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1622,7 +1502,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Liten glänta och intill körvägar i sandtallskog.</t>
+          <t>Solexponerad, gammal körväg på sandig mark.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1637,6 +1517,123 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>87235164</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101348</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>224913</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vanlig backsippa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Pulsatilla vulgaris subsp. vulgaris</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Skoklosters NR, vid Dampeboda, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>645455</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6623988</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Håbo</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Skokloster</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2020-05-15</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2020-05-15</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>267 stjälkar (de flesta blommande, men även i knopp och överblommade), i och vid en liten glänta och intill ett par körvägar i sandtallskog.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Liten glänta och intill körvägar i sandtallskog.</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22010-2025 artfynd.xlsx
+++ b/artfynd/A 22010-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/333192</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3925186</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6748708</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6748698</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1192,6 +1217,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6748697</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1304,6 +1334,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6296611</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1400,6 +1435,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6748701</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1517,6 +1557,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87235164</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1634,8 +1679,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87235162</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>